--- a/job_application_forms/015_facebook_ad_marketer_recruitment_form--job_application_forms.xlsx
+++ b/job_application_forms/015_facebook_ad_marketer_recruitment_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'archived'}</t>
+          <t>archived</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Archived'}</t>
+          <t>Archived</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one_day'}</t>
+          <t>one_day</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'One Day'}</t>
+          <t>One Day</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'two_days'}</t>
+          <t>two_days</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Two Days'}</t>
+          <t>Two Days</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'multiple_days'}</t>
+          <t>multiple_days</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Multiple Days'}</t>
+          <t>Multiple Days</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'display_ad'}</t>
+          <t>display_ad</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Display Ad'}</t>
+          <t>Display Ad</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'video_ad'}</t>
+          <t>video_ad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Video Ad'}</t>
+          <t>Video Ad</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'carousel_ad'}</t>
+          <t>carousel_ad</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Carousel Ad'}</t>
+          <t>Carousel Ad</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'men'}</t>
+          <t>men</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Men'}</t>
+          <t>Men</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'women'}</t>
+          <t>women</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Women'}</t>
+          <t>Women</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'united_states'}</t>
+          <t>united_states</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'United States'}</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'canada'}</t>
+          <t>canada</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Canada'}</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'worldwide'}</t>
+          <t>worldwide</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Worldwide'}</t>
+          <t>Worldwide</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '18-24'}</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '25-34'}</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '35-44'}</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '45-54'}</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'55+'}</t>
+          <t>55+</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '55+'}</t>
+          <t>55+</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'USD'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'eur'}</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'EUR'}</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
